--- a/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0553</v>
+        <v>0.0559</v>
       </c>
       <c r="E2">
-        <v>0.0111</v>
+        <v>-0.0761</v>
       </c>
       <c r="G2">
-        <v>0.04502481890095241</v>
+        <v>0.01560965835086665</v>
       </c>
       <c r="H2">
-        <v>0.04502481890095241</v>
+        <v>0.01560965835086665</v>
       </c>
       <c r="I2">
-        <v>0.03129110904530546</v>
+        <v>-0.0203586814948402</v>
       </c>
       <c r="J2">
-        <v>0.02251536758051487</v>
+        <v>-0.01606963342710701</v>
       </c>
       <c r="K2">
-        <v>132.9</v>
+        <v>84.3</v>
       </c>
       <c r="L2">
-        <v>0.02331047305000614</v>
+        <v>0.01689209498046288</v>
       </c>
       <c r="M2">
-        <v>38.9763</v>
+        <v>36.3255</v>
       </c>
       <c r="N2">
-        <v>0.049051472438963</v>
+        <v>0.05661705112219451</v>
       </c>
       <c r="O2">
-        <v>0.29327539503386</v>
+        <v>0.4309074733096085</v>
       </c>
       <c r="P2">
-        <v>38.9763</v>
+        <v>36.3255</v>
       </c>
       <c r="Q2">
-        <v>0.049051472438963</v>
+        <v>0.05661705112219451</v>
       </c>
       <c r="R2">
-        <v>0.29327539503386</v>
+        <v>0.4309074733096085</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,28 +639,28 @@
         <v>0.001</v>
       </c>
       <c r="V2">
-        <v>1.258494840171155e-06</v>
+        <v>1.55860349127182e-06</v>
       </c>
       <c r="W2">
-        <v>0.06297682793915557</v>
+        <v>0.0395718912829179</v>
       </c>
       <c r="X2">
-        <v>0.07981750924384215</v>
+        <v>0.1128073575902376</v>
       </c>
       <c r="Y2">
-        <v>-0.01684068130468658</v>
+        <v>-0.07323546630731965</v>
       </c>
       <c r="Z2">
-        <v>2.701656353747196</v>
+        <v>2.342628898572454</v>
       </c>
       <c r="AA2">
-        <v>0.0608287858808516</v>
+        <v>-0.03764518765580677</v>
       </c>
       <c r="AB2">
-        <v>0.07981750924384215</v>
+        <v>0.1128073575902376</v>
       </c>
       <c r="AC2">
-        <v>-0.01898872336299055</v>
+        <v>-0.1504525452460443</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -681,28 +681,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-1.258496423982411e-06</v>
+        <v>-1.55860592052045e-06</v>
       </c>
       <c r="AK2">
-        <v>-4.694176732937489e-07</v>
+        <v>-5.247969167131549e-07</v>
       </c>
       <c r="AL2">
-        <v>0.284</v>
+        <v>0.223</v>
       </c>
       <c r="AM2">
-        <v>0.284</v>
+        <v>0.223</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>628.1690140845071</v>
+        <v>-455.6053811659193</v>
       </c>
       <c r="AP2">
-        <v>-5.385029617662898e-06</v>
+        <v>1.086956521739131e-05</v>
       </c>
       <c r="AQ2">
-        <v>628.1690140845071</v>
+        <v>-455.6053811659193</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0553</v>
+        <v>0.0559</v>
       </c>
       <c r="E3">
-        <v>0.0111</v>
+        <v>-0.0761</v>
       </c>
       <c r="G3">
-        <v>0.04502481890095241</v>
+        <v>0.01560965835086665</v>
       </c>
       <c r="H3">
-        <v>0.04502481890095241</v>
+        <v>0.01560965835086665</v>
       </c>
       <c r="I3">
-        <v>0.03129110904530546</v>
+        <v>-0.0203586814948402</v>
       </c>
       <c r="J3">
-        <v>0.02251536758051487</v>
+        <v>-0.01606963342710701</v>
       </c>
       <c r="K3">
-        <v>132.9</v>
+        <v>84.3</v>
       </c>
       <c r="L3">
-        <v>0.02331047305000614</v>
+        <v>0.01689209498046288</v>
       </c>
       <c r="M3">
-        <v>38.9763</v>
+        <v>36.3255</v>
       </c>
       <c r="N3">
-        <v>0.049051472438963</v>
+        <v>0.05661705112219451</v>
       </c>
       <c r="O3">
-        <v>0.29327539503386</v>
+        <v>0.4309074733096085</v>
       </c>
       <c r="P3">
-        <v>38.9763</v>
+        <v>36.3255</v>
       </c>
       <c r="Q3">
-        <v>0.049051472438963</v>
+        <v>0.05661705112219451</v>
       </c>
       <c r="R3">
-        <v>0.29327539503386</v>
+        <v>0.4309074733096085</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,28 +773,28 @@
         <v>0.001</v>
       </c>
       <c r="V3">
-        <v>1.258494840171155e-06</v>
+        <v>1.55860349127182e-06</v>
       </c>
       <c r="W3">
-        <v>0.06297682793915557</v>
+        <v>0.0395718912829179</v>
       </c>
       <c r="X3">
-        <v>0.07981750924384215</v>
+        <v>0.1128073575902376</v>
       </c>
       <c r="Y3">
-        <v>-0.01684068130468658</v>
+        <v>-0.07323546630731965</v>
       </c>
       <c r="Z3">
-        <v>2.701656353747196</v>
+        <v>2.342628898572454</v>
       </c>
       <c r="AA3">
-        <v>0.0608287858808516</v>
+        <v>-0.03764518765580677</v>
       </c>
       <c r="AB3">
-        <v>0.07981750924384215</v>
+        <v>0.1128073575902376</v>
       </c>
       <c r="AC3">
-        <v>-0.01898872336299055</v>
+        <v>-0.1504525452460443</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -815,28 +815,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.258496423982411e-06</v>
+        <v>-1.55860592052045e-06</v>
       </c>
       <c r="AK3">
-        <v>-4.694176732937489e-07</v>
+        <v>-5.247969167131549e-07</v>
       </c>
       <c r="AL3">
-        <v>0.284</v>
+        <v>0.223</v>
       </c>
       <c r="AM3">
-        <v>0.284</v>
+        <v>0.223</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>628.1690140845071</v>
+        <v>-455.6053811659193</v>
       </c>
       <c r="AP3">
-        <v>-5.385029617662898e-06</v>
+        <v>1.086956521739131e-05</v>
       </c>
       <c r="AQ3">
-        <v>628.1690140845071</v>
+        <v>-455.6053811659193</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0559</v>
+        <v>0.0537</v>
       </c>
       <c r="E2">
-        <v>-0.0761</v>
+        <v>0.334</v>
       </c>
       <c r="G2">
-        <v>0.01560965835086665</v>
+        <v>0.02422645051810665</v>
       </c>
       <c r="H2">
-        <v>0.01560965835086665</v>
+        <v>0.02422645051810665</v>
       </c>
       <c r="I2">
-        <v>-0.0203586814948402</v>
+        <v>0.08107376250135395</v>
       </c>
       <c r="J2">
-        <v>-0.01606963342710701</v>
+        <v>0.06339455948337326</v>
       </c>
       <c r="K2">
-        <v>84.3</v>
+        <v>227.7</v>
       </c>
       <c r="L2">
-        <v>0.01689209498046288</v>
+        <v>0.04110553489547605</v>
       </c>
       <c r="M2">
-        <v>36.3255</v>
+        <v>38.1976</v>
       </c>
       <c r="N2">
-        <v>0.05661705112219451</v>
+        <v>0.04786666666666667</v>
       </c>
       <c r="O2">
-        <v>0.4309074733096085</v>
+        <v>0.167754062362758</v>
       </c>
       <c r="P2">
-        <v>36.3255</v>
+        <v>38.1976</v>
       </c>
       <c r="Q2">
-        <v>0.05661705112219451</v>
+        <v>0.04786666666666667</v>
       </c>
       <c r="R2">
-        <v>0.4309074733096085</v>
+        <v>0.167754062362758</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.55860349127182e-06</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.0395718912829179</v>
+        <v>0.1194961952243506</v>
       </c>
       <c r="X2">
-        <v>0.1128073575902376</v>
+        <v>0.09577231143683715</v>
       </c>
       <c r="Y2">
-        <v>-0.07323546630731965</v>
+        <v>0.0237238837875134</v>
       </c>
       <c r="Z2">
-        <v>2.342628898572454</v>
+        <v>2.90706004044085</v>
       </c>
       <c r="AA2">
-        <v>-0.03764518765580677</v>
+        <v>0.1842917906554649</v>
       </c>
       <c r="AB2">
-        <v>0.1128073575902376</v>
+        <v>0.09577231143683715</v>
       </c>
       <c r="AC2">
-        <v>-0.1504525452460443</v>
+        <v>0.08851947921862779</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,28 +681,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-1.55860592052045e-06</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>-5.247969167131549e-07</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>0.223</v>
+        <v>0.327</v>
       </c>
       <c r="AM2">
-        <v>0.223</v>
+        <v>0.327</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-455.6053811659193</v>
+        <v>1373.394495412844</v>
       </c>
       <c r="AP2">
-        <v>1.086956521739131e-05</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-455.6053811659193</v>
+        <v>1373.394495412844</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0559</v>
+        <v>0.0537</v>
       </c>
       <c r="E3">
-        <v>-0.0761</v>
+        <v>0.334</v>
       </c>
       <c r="G3">
-        <v>0.01560965835086665</v>
+        <v>0.02422645051810665</v>
       </c>
       <c r="H3">
-        <v>0.01560965835086665</v>
+        <v>0.02422645051810665</v>
       </c>
       <c r="I3">
-        <v>-0.0203586814948402</v>
+        <v>0.08107376250135395</v>
       </c>
       <c r="J3">
-        <v>-0.01606963342710701</v>
+        <v>0.06339455948337326</v>
       </c>
       <c r="K3">
-        <v>84.3</v>
+        <v>227.7</v>
       </c>
       <c r="L3">
-        <v>0.01689209498046288</v>
+        <v>0.04110553489547605</v>
       </c>
       <c r="M3">
-        <v>36.3255</v>
+        <v>38.1976</v>
       </c>
       <c r="N3">
-        <v>0.05661705112219451</v>
+        <v>0.04786666666666667</v>
       </c>
       <c r="O3">
-        <v>0.4309074733096085</v>
+        <v>0.167754062362758</v>
       </c>
       <c r="P3">
-        <v>36.3255</v>
+        <v>38.1976</v>
       </c>
       <c r="Q3">
-        <v>0.05661705112219451</v>
+        <v>0.04786666666666667</v>
       </c>
       <c r="R3">
-        <v>0.4309074733096085</v>
+        <v>0.167754062362758</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.55860349127182e-06</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.0395718912829179</v>
+        <v>0.1194961952243506</v>
       </c>
       <c r="X3">
-        <v>0.1128073575902376</v>
+        <v>0.09577231143683715</v>
       </c>
       <c r="Y3">
-        <v>-0.07323546630731965</v>
+        <v>0.0237238837875134</v>
       </c>
       <c r="Z3">
-        <v>2.342628898572454</v>
+        <v>2.90706004044085</v>
       </c>
       <c r="AA3">
-        <v>-0.03764518765580677</v>
+        <v>0.1842917906554649</v>
       </c>
       <c r="AB3">
-        <v>0.1128073575902376</v>
+        <v>0.09577231143683715</v>
       </c>
       <c r="AC3">
-        <v>-0.1504525452460443</v>
+        <v>0.08851947921862779</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,28 +815,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.55860592052045e-06</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>-5.247969167131549e-07</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.223</v>
+        <v>0.327</v>
       </c>
       <c r="AM3">
-        <v>0.223</v>
+        <v>0.327</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-455.6053811659193</v>
+        <v>1373.394495412844</v>
       </c>
       <c r="AP3">
-        <v>1.086956521739131e-05</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-455.6053811659193</v>
+        <v>1373.394495412844</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0537</v>
+        <v>-0.0654</v>
       </c>
       <c r="E2">
-        <v>0.334</v>
+        <v>0.132</v>
       </c>
       <c r="G2">
-        <v>0.02422645051810665</v>
+        <v>0.1104567307692308</v>
       </c>
       <c r="H2">
-        <v>0.02422645051810665</v>
+        <v>0.1104567307692308</v>
       </c>
       <c r="I2">
-        <v>0.08107376250135395</v>
+        <v>0.1134314903846154</v>
       </c>
       <c r="J2">
-        <v>0.06339455948337326</v>
+        <v>0.09745970084534555</v>
       </c>
       <c r="K2">
-        <v>227.7</v>
+        <v>245.2</v>
       </c>
       <c r="L2">
-        <v>0.04110553489547605</v>
+        <v>0.07367788461538462</v>
       </c>
       <c r="M2">
-        <v>38.1976</v>
+        <v>72.75030000000001</v>
       </c>
       <c r="N2">
-        <v>0.04786666666666667</v>
+        <v>0.06373777816716314</v>
       </c>
       <c r="O2">
-        <v>0.167754062362758</v>
+        <v>0.2966977977161501</v>
       </c>
       <c r="P2">
-        <v>38.1976</v>
+        <v>72.75030000000001</v>
       </c>
       <c r="Q2">
-        <v>0.04786666666666667</v>
+        <v>0.06373777816716314</v>
       </c>
       <c r="R2">
-        <v>0.167754062362758</v>
+        <v>0.2966977977161501</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>8.761170492377781E-07</v>
       </c>
       <c r="W2">
-        <v>0.1194961952243506</v>
+        <v>0.1038895008897551</v>
       </c>
       <c r="X2">
-        <v>0.09577231143683715</v>
+        <v>0.09923561471287171</v>
       </c>
       <c r="Y2">
-        <v>0.0237238837875134</v>
+        <v>0.004653886176883407</v>
       </c>
       <c r="Z2">
-        <v>2.90706004044085</v>
+        <v>1.410049995763071</v>
       </c>
       <c r="AA2">
-        <v>0.1842917906554649</v>
+        <v>0.1374230507640497</v>
       </c>
       <c r="AB2">
-        <v>0.09577231143683715</v>
+        <v>0.09923561471287171</v>
       </c>
       <c r="AC2">
-        <v>0.08851947921862779</v>
+        <v>0.03818743605117797</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,28 +681,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>-8.761178168195346E-07</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>-3.888933611625423E-07</v>
       </c>
       <c r="AL2">
-        <v>0.327</v>
+        <v>0.335</v>
       </c>
       <c r="AM2">
-        <v>0.327</v>
+        <v>0.335</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>1373.394495412844</v>
+        <v>1126.865671641791</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>-2.522704339051463E-06</v>
       </c>
       <c r="AQ2">
-        <v>1373.394495412844</v>
+        <v>1126.865671641791</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0537</v>
+        <v>-0.0654</v>
       </c>
       <c r="E3">
-        <v>0.334</v>
+        <v>0.132</v>
       </c>
       <c r="G3">
-        <v>0.02422645051810665</v>
+        <v>0.1104567307692308</v>
       </c>
       <c r="H3">
-        <v>0.02422645051810665</v>
+        <v>0.1104567307692308</v>
       </c>
       <c r="I3">
-        <v>0.08107376250135395</v>
+        <v>0.1134314903846154</v>
       </c>
       <c r="J3">
-        <v>0.06339455948337326</v>
+        <v>0.09745970084534555</v>
       </c>
       <c r="K3">
-        <v>227.7</v>
+        <v>245.2</v>
       </c>
       <c r="L3">
-        <v>0.04110553489547605</v>
+        <v>0.07367788461538462</v>
       </c>
       <c r="M3">
-        <v>38.1976</v>
+        <v>72.75030000000001</v>
       </c>
       <c r="N3">
-        <v>0.04786666666666667</v>
+        <v>0.06373777816716314</v>
       </c>
       <c r="O3">
-        <v>0.167754062362758</v>
+        <v>0.2966977977161501</v>
       </c>
       <c r="P3">
-        <v>38.1976</v>
+        <v>72.75030000000001</v>
       </c>
       <c r="Q3">
-        <v>0.04786666666666667</v>
+        <v>0.06373777816716314</v>
       </c>
       <c r="R3">
-        <v>0.167754062362758</v>
+        <v>0.2966977977161501</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>8.761170492377781E-07</v>
       </c>
       <c r="W3">
-        <v>0.1194961952243506</v>
+        <v>0.1038895008897551</v>
       </c>
       <c r="X3">
-        <v>0.09577231143683715</v>
+        <v>0.09923561471287171</v>
       </c>
       <c r="Y3">
-        <v>0.0237238837875134</v>
+        <v>0.004653886176883407</v>
       </c>
       <c r="Z3">
-        <v>2.90706004044085</v>
+        <v>1.410049995763071</v>
       </c>
       <c r="AA3">
-        <v>0.1842917906554649</v>
+        <v>0.1374230507640497</v>
       </c>
       <c r="AB3">
-        <v>0.09577231143683715</v>
+        <v>0.09923561471287171</v>
       </c>
       <c r="AC3">
-        <v>0.08851947921862779</v>
+        <v>0.03818743605117797</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,28 +815,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-8.761178168195346E-07</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-3.888933611625423E-07</v>
       </c>
       <c r="AL3">
-        <v>0.327</v>
+        <v>0.335</v>
       </c>
       <c r="AM3">
-        <v>0.327</v>
+        <v>0.335</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>1373.394495412844</v>
+        <v>1126.865671641791</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-2.522704339051463E-06</v>
       </c>
       <c r="AQ3">
-        <v>1373.394495412844</v>
+        <v>1126.865671641791</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/south_korea/south_korea_reinsurance.xlsx
@@ -645,10 +645,10 @@
         <v>0.1038895008897551</v>
       </c>
       <c r="X2">
-        <v>0.09923561471287171</v>
+        <v>0.09920921995563164</v>
       </c>
       <c r="Y2">
-        <v>0.004653886176883407</v>
+        <v>0.004680280934123468</v>
       </c>
       <c r="Z2">
         <v>1.410049995763071</v>
@@ -657,10 +657,10 @@
         <v>0.1374230507640497</v>
       </c>
       <c r="AB2">
-        <v>0.09923561471287171</v>
+        <v>0.09920921995563164</v>
       </c>
       <c r="AC2">
-        <v>0.03818743605117797</v>
+        <v>0.03821383080841803</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -779,10 +779,10 @@
         <v>0.1038895008897551</v>
       </c>
       <c r="X3">
-        <v>0.09923561471287171</v>
+        <v>0.09920921995563164</v>
       </c>
       <c r="Y3">
-        <v>0.004653886176883407</v>
+        <v>0.004680280934123468</v>
       </c>
       <c r="Z3">
         <v>1.410049995763071</v>
@@ -791,10 +791,10 @@
         <v>0.1374230507640497</v>
       </c>
       <c r="AB3">
-        <v>0.09923561471287171</v>
+        <v>0.09920921995563164</v>
       </c>
       <c r="AC3">
-        <v>0.03818743605117797</v>
+        <v>0.03821383080841803</v>
       </c>
       <c r="AD3">
         <v>0</v>
